--- a/extenbooks/S1606_extenbook.xlsx
+++ b/extenbooks/S1606_extenbook.xlsx
@@ -2635,7 +2635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -3901,11 +3901,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3928,76 +3928,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Household Debt-Service Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension_deferred", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1606_research.json", "adequacy_report": "Technical/docs/chapters/CH16_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1606_DPR.md", "epr": "Technical/docs/series/S1606_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1606_load.py", "processor": "Technical/code/P02_processors/P02_S1606_construct.py", "validator": "Technical/code/V03_validators/V03_S1606_validate.py", "processed": "Technical/data/processed/S1606.parquet", "chopped_csv": "Technical/chopped/S1606.csv", "extenbook_xlsx": "Technical/extenbooks/S1606_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:17:23.977169+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1606_extenbook.xlsx
+++ b/extenbooks/S1606_extenbook.xlsx
@@ -2582,7 +2582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A167"/>
+  <dimension ref="A1:A162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2689,21 +2689,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>**Dual-frequency emission (Phase 4 ratified)**:</t>
+          <t>**Emission cadence**: the shipped chopped emits the **annual mean** of the quarterly Fed series (33 obs per subseries, 1980-2012), consistent with the annual cadence used across Chapter 16. The underlying book figure (Fig 16.10) is quarterly; a quarterly emission and the FRED extension to 2024 are **deferred to Phase 6** (see §3). (Note: the registry declares `native_units: decimal_quarterly` for S1606-A/-B while the shipped chopped is `decimal_annual_mean_of_quarterly` — flagged for the registry owner; DF-2 does not touch the registry.)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- **Primary**: quarterly (book-faithful — matches Fig 16.10 x-axis)</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>- **Secondary**: annual average (cross-Ch16 cadence consistency for downstream tooling)</t>
+          <t>## 2. Why it matters in Chapter 16</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2709,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>## 2. Why it matters in Chapter 16</t>
+          <t>Higher debt loads imply higher debt-service burdens, but for two decades after 1980 falling interest rates offset rising debt — the debt-service ratio in 2000 was no higher than in 1985 (Shaikh 2016, p. 735). The post-2000 surge in S1606 reflects the moment when even falling rates could no longer offset the debt accumulation, presaging the 2007 default cascade. S1606 is the chapter's most direct empirical link to the proximate cause of the 2007 crisis.</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Higher debt loads imply higher debt-service burdens, but for two decades after 1980 falling interest rates offset rising debt — the debt-service ratio in 2000 was no higher than in 1985 (Shaikh 2016, p. 735). The post-2000 surge in S1606 reflects the moment when even falling rates could no longer offset the debt accumulation, presaging the 2007 default cascade. S1606 is the chapter's most direct empirical link to the proximate cause of the 2007 crisis.</t>
+          <t>## 3. Sources (per subseries)</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2729,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>## 3. Sources (per subseries)</t>
+          <t>The shipped chopped carries **two book-period subseries (A, B — both annual means, 1980-2012, 33 obs each, sourced from `SHAIKH_APPENDIX_16_2`)**:</t>
         </is>
       </c>
     </row>
@@ -2757,70 +2753,70 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| **S1606-A** | 1980Q1-2012Q4 | Shaikh Appendix 16.2 — `Financial obligations ratio, seasonally adjusted` (FOR) | decimal | Salvaged xlsx |</t>
+          <t>| **S1606-A** | 1980-2012 (annual, 33 obs) | Shaikh Appendix 16.2 — `Financial obligations ratio, seasonally adjusted` (FOR), annual mean of the four quarters | decimal (annual mean of quarterly) | Salvaged xlsx |</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| **S1606-B** | 1980Q1-2012Q4 | Shaikh Appendix 16.2 — `Debt service ratio, seasonally adjusted` (DSR) | decimal | Salvaged xlsx |</t>
+          <t>| **S1606-B** | 1980-2012 (annual, 33 obs) | Shaikh Appendix 16.2 — `Debt service ratio, seasonally adjusted` (DSR), annual mean of the four quarters | decimal (annual mean of quarterly) | Salvaged xlsx |</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| **S1606-C** | 2013Q1-2024Q4 | FRED `FODSP` (FOR Financial Obligations Ratio, quarterly SA) extension | percent | FRED API |</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| **S1606-D** | 2013Q1-2024Q4 | FRED `TDSP` (DSR Household Debt Service Ratio, quarterly SA) extension | percent | FRED API |</t>
+          <t>**No separate lettered annual variant exists** — the annual mean *is* S1606-A/-B as shipped (there is no phantom S1606-E). **Extensions deferred to Phase 6 (NOT shipped):** the FRED `FODSP` (FOR) and FRED `TDSP` (DSR) quarterly extensions to 2024 (earlier drafted as S1606-C/-D) are declared `extension_deferred_to_phase6: true` and are absent from the shipped chopped. The Fed identifier in the book (`FOR/FOR/DTFD%YPD.Q`) is the legacy DDP name; FRED `TDSP` and `FODSP` are the modern public mirrors that a Phase-6 extension would use. (Corrected 2026-07-02, campaign DF-2.)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>| **S1606-E** | 1980-2024 (annual) | Quarterly-averaged TDSP/FODSP annual mean (secondary variant) | percent | Computed |</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>The Fed identifier in the book (`FOR/FOR/DTFD%YPD.Q`) is the legacy DDP name; FRED `TDSP` and `FODSP` are the modern public mirrors.</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S1606 as shipped is **direct**: the annual value for each subseries is the simple mean of the four quarterly Appendix 16.2 observations:</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S1606 is **direct** at quarterly cadence (single Fed-published series per subseries, no transformation other than concatenation across the splice). For the secondary annual variant:</t>
+          <t>annual_mean_t = mean( quarterly_value_{t,Q1}, quarterly_value_{t,Q2},</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      quarterly_value_{t,Q3}, quarterly_value_{t,Q4} )</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2830,77 +2826,73 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>annual_mean_t = mean( quarterly_value_{t,Q1}, quarterly_value_{t,Q2},</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      quarterly_value_{t,Q3}, quarterly_value_{t,Q4} )</t>
+          <t>**Unit alignment**: Appendix 16.2 stores ratios in decimal form (0.111 = 11.1%). FRED publishes the same series in percent (11.1); a Phase-6 extension loader would convert FRED percent -&gt; decimal so book and extension values match in cadence and units.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>**Unit alignment**: Appendix 16.2 stores ratios in decimal form (0.111 = 11.1%). FRED publishes the same series in percent (11.1). The loader converts FRED percent -&gt; decimal during ingestion so book and extension values match in cadence and units.</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>- **Book period**: 1980-2012 (annual, 33 obs per subseries as shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>- **Extension period**: deferred to Phase 6 (FRED TDSP/FODSP quarterly to 2024 not yet shipped)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>- **Total shipped**: 1980-2012 (annual; 66 rows across A+B)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>- **Book period**: 1980Q1-2012Q4 (132 quarterly obs per subseries)</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>- **Extension period**: 2013Q1-2024Q4 (~48 quarterly obs)</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>- **Total**: 1980Q1-2024Q4 (~180 obs primary; ~45 obs annual secondary)</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>- **Shipped (annual)**: decimal annual mean of quarterly values (e.g. 0.111 = 11.1% of DPI)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- Fig 16.10 chart axis: percent (book convention is decimal × 100)</t>
         </is>
       </c>
     </row>
@@ -2910,283 +2902,283 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>- **Primary (quarterly)**: decimal (e.g. 0.111 = 11.1% of DPI)</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>- **Secondary (annual)**: decimal annual mean of quarterly values</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>- Fig 16.10 chart axis: percent (book convention is decimal × 100)</t>
+          <t>1. **FOR &gt; DSR by construction.** Financial Obligations Ratio adds rent, auto leases, homeowner's insurance, and property tax to the debt-service base. Numerically FOR is always larger than DSR. Both series are emitted because Shaikh plots both at various points.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2. **Quarterly to annual aggregation**. The shipped annual series uses simple-mean of the four quarters, not end-of-period or weighted. Documented per the book's apparent convention (no explicit aggregation rule in Appendix 16.1).</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>3. **Direct continuation, no proxy.** TDSP and FODSP are the exact Fed-published series the book cites under the legacy DDP identifier `FOR/FOR/DTFD%YPD.Q`. Same agency, same release, same concept. `proxy: false`.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4. **Quarterly seasonality preserved.** Fed publishes SA versions; we use them directly. No additional X-13 seasonal adjustment.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1. **FOR &gt; DSR by construction.** Financial Obligations Ratio adds rent, auto leases, homeowner's insurance, and property tax to the debt-service base. Numerically FOR is always larger than DSR. Both series are emitted because Shaikh plots both at various points.</t>
+          <t>5. **Unit conversion FRED -&gt; book**: FRED is percent (11.1), book Appendix is decimal (0.111). The loader divides by 100 to align.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2. **Quarterly to annual aggregation**. The secondary annual variant uses simple-mean of the four quarters, not end-of-period or weighted. Documented per the book's apparent convention (no explicit aggregation rule in Appendix 16.1).</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3. **Direct continuation, no proxy.** TDSP and FODSP are the exact Fed-published series the book cites under the legacy DDP identifier `FOR/FOR/DTFD%YPD.Q`. Same agency, same release, same concept. `proxy: false`.</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>4. **Quarterly seasonality preserved.** Fed publishes SA versions; we use them directly. No additional X-13 seasonal adjustment.</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5. **Unit conversion FRED -&gt; book**: FRED is percent (11.1), book Appendix is decimal (0.111). The loader divides by 100 to align.</t>
+          <t>- **CD legacy ID**: `S101`</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>- **CD2 legacy ID**: `S101` (2 subseries A-B)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S101_*`</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>- **Book reference**: Shaikh (2016), Ch. 16, p. 735-736 (Fig 16.10); Appendix 16.1 p. 899; Appendix 16.2 HouseholdDebtService sheet</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S101`</t>
+          <t>- **Paired with**: S1605 (Household Debt-to-Income Ratio) — same DPI denominator, parallel narrative</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>- **CD2 legacy ID**: `S101` (2 subseries A-B)</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S101_*`</t>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 16, p. 735-736 (Fig 16.10); Appendix 16.1 p. 899; Appendix 16.2 HouseholdDebtService sheet</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>- **Paired with**: S1605 (Household Debt-to-Income Ratio) — same DPI denominator, parallel narrative</t>
+          <t>- **Tolerance**: ±1.0% per year on S1606-A (FOR) and S1606-B (DSR) against the annual means of the Appendix 16.2 columns over 1980-2012.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **Expected MAE**: ~0% (annual mean computed directly from the book quarterly columns).</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Sample-year benchmarks (per CD2 S101 validation table)**: 1980, 1985, 2000, 2007, 2012 — annual means cross-checked against book.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>- **Tolerance**: ±1.0% per quarter on S1606-A (FOR) and S1606-B (DSR) against Appendix 16.2 columns over 1980Q1-2012Q4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>- **Expected MAE**: ~0% (we read the book column directly into the book-period parquet).</t>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- **FOR &gt; DSR ordering**: assertion `S1606-A[t] &gt;= S1606-B[t]` at every year (FOR always exceeds DSR by construction).</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>- **Sample-quarter benchmarks (per CD2 S101 validation table)**: 1980Q1, 1985Q1, 2000Q1, 2007Q1, 2012Q1 — values cross-checked against book.</t>
-        </is>
+      <c r="A82" s="4">
+        <f>== EPR: S1606_EPR.md ===</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>- **FOR &gt; DSR ordering**: assertion `S1606-A[t] &gt;= S1606-B[t]` at every quarter (FOR always exceeds DSR by construction).</t>
+          <t># S1606 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>- **Annual secondary variant**: validated as exact mean of corresponding quarterly observations.</t>
+      <c r="A84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>**Series**: S1606 — Household Debt-Service Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4">
-        <f>== EPR: S1606_EPR.md ===</f>
-        <v/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `direct`</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t># S1606 — Extension Provenance Record</t>
+          <t>**Extension method**: direct continuation via FRED `TDSP` and `FODSP` (the modern public mirrors of the Fed legacy DDP series the book cites); emit both quarterly (primary) and annual-mean (secondary) variants</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>**Series**: S1606 — Household Debt-Service Ratio</t>
+          <t>**Author**: opus-subagent-ch16-fanout</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>**Construction classification**: `direct`</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>**Extension method**: direct continuation via FRED `TDSP` and `FODSP` (the modern public mirrors of the Fed legacy DDP series the book cites); emit both quarterly (primary) and annual-mean (secondary) variants</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch16-fanout</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>`time_series`. The Federal Reserve continues to publish the Household Debt Service and Financial Obligations Ratios quarterly without interruption since 1980. FRED republishes the two ratios as `TDSP` (DSR) and `FODSP` (FOR). No methodology change since 1980.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>## 2. Construction classification</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>## 1. Why this series is extendable</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>`direct` — single-source per subseries, no algebraic combination. Lazy-splice prohibition does not apply because the extension uses the *exact same observed series* the book cites (Fed legacy DDP `FOR/FOR/DTFD%YPD.Q` -&gt; FRED `TDSP`).</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>`time_series`. The Federal Reserve continues to publish the Household Debt Service and Financial Obligations Ratios quarterly without interruption since 1980. FRED republishes the two ratios as `TDSP` (DSR) and `FODSP` (FOR). No methodology change since 1980.</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>## 3. Method</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>## 2. Construction classification</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>`direct` — single-source per subseries, no algebraic combination. Lazy-splice prohibition does not apply because the extension uses the *exact same observed series* the book cites (Fed legacy DDP `FOR/FOR/DTFD%YPD.Q` -&gt; FRED `TDSP`).</t>
+          <t>INPUTS (each extension run, TTL=30d)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FRED TDSP   quarterly SA, percent</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t xml:space="preserve">  FRED FODSP  quarterly SA, percent</t>
         </is>
       </c>
     </row>
@@ -3196,347 +3188,316 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>UNIT CONVERSION (FRED -&gt; book scale)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INPUTS (each extension run, TTL=30d)</t>
+          <t xml:space="preserve">  tdsp_decimal_t  = TDSP_t  / 100.0     # 11.1 -&gt; 0.111</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FRED TDSP   quarterly SA, percent</t>
+          <t xml:space="preserve">  fodsp_decimal_t = FODSP_t / 100.0</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FRED FODSP  quarterly SA, percent</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SPLICE (primary quarterly variant)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UNIT CONVERSION (FRED -&gt; book scale)</t>
+          <t xml:space="preserve">  S1606-A_extended[t] = book FOR[t]      for t in [1980Q1, 2012Q4]</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">  tdsp_decimal_t  = TDSP_t  / 100.0     # 11.1 -&gt; 0.111</t>
+          <t xml:space="preserve">  S1606-A_extended[t] = fodsp_decimal_t  for t in [2013Q1, 2024Q4]</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fodsp_decimal_t = FODSP_t / 100.0</t>
+          <t xml:space="preserve">  S1606-B_extended[t] = book DSR[t]      for t in [1980Q1, 2012Q4]</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S1606-B_extended[t] = tdsp_decimal_t   for t in [2013Q1, 2024Q4]</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>SPLICE (primary quarterly variant)</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1606-A_extended[t] = book FOR[t]      for t in [1980Q1, 2012Q4]</t>
+          <t>ANNUAL VARIANT (secondary)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1606-A_extended[t] = fodsp_decimal_t  for t in [2013Q1, 2024Q4]</t>
+          <t xml:space="preserve">  S1606-A_annual[year] = mean( S1606-A_extended[year-Q1..Q4] )</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1606-B_extended[t] = book DSR[t]      for t in [1980Q1, 2012Q4]</t>
+          <t xml:space="preserve">  S1606-B_annual[year] = mean( S1606-B_extended[year-Q1..Q4] )</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S1606-B_extended[t] = tdsp_decimal_t   for t in [2013Q1, 2024Q4]</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>OUTPUT</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ANNUAL VARIANT (secondary)</t>
+          <t xml:space="preserve">  Primary parquet (quarterly):  Technical/data/processed/S1606.parquet</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1606-A_annual[year] = mean( S1606-A_extended[year-Q1..Q4] )</t>
+          <t xml:space="preserve">                                  columns: year, quarter, qdate, value, subseries_id, source_id, units</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1606-B_annual[year] = mean( S1606-B_extended[year-Q1..Q4] )</t>
+          <t xml:space="preserve">  Secondary parquet (annual):   Technical/data/processed/S1606_annual.parquet</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  columns: year, value, subseries_id, source_id, units</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OUTPUT</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Primary parquet (quarterly):  Technical/data/processed/S1606.parquet</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  columns: year, quarter, qdate, value, subseries_id, source_id, units</t>
+          <t>## 4. Component re-fetching</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Secondary parquet (annual):   Technical/data/processed/S1606_annual.parquet</t>
-        </is>
-      </c>
+      <c r="A131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  columns: year, value, subseries_id, source_id, units</t>
+          <t>Every extension run re-pulls TDSP and FODSP from FRED at quarterly frequency. The annual variant is a deterministic average; recomputed from scratch each run (never persisted across runs without recompute).</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>## 5. Proxies</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>## 4. Component re-fetching</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>**None.** TDSP = the book's `DTFD%YPD.Q` identifier under FRED's modern naming. FODSP is the parallel FOR series cited in CD2 and tracked here. Both are direct Fed-published series. `proxy: false` on all subseries.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Every extension run re-pulls TDSP and FODSP from FRED at quarterly frequency. The annual variant is a deterministic average; recomputed from scratch each run (never persisted across runs without recompute).</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>## 6. Synthetic data</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>## 5. Proxies</t>
-        </is>
-      </c>
+      <c r="A139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>**None permitted.** If FRED returns NaN for any quarter, the value is NaN in S1606. Annual variant tolerates up to 1 NaN quarter (averages over remaining); if 2 or more NaN, the annual value is NaN.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>**None.** TDSP = the book's `DTFD%YPD.Q` identifier under FRED's modern naming. FODSP is the parallel FOR series cited in CD2 and tracked here. Both are direct Fed-published series. `proxy: false` on all subseries.</t>
-        </is>
-      </c>
+      <c r="A141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>## 7. Failure modes &amp; graceful degradation</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>## 6. Synthetic data</t>
-        </is>
-      </c>
+      <c r="A143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Action |</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>**None permitted.** If FRED returns NaN for any quarter, the value is NaN in S1606. Annual variant tolerates up to 1 NaN quarter (averages over remaining); if 2 or more NaN, the annual value is NaN.</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>| FRED_API_KEY missing | startup | Extension skipped; book quarterly published only |</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>## 7. Failure modes &amp; graceful degradation</t>
+          <t>| TDSP / FODSP 5xx | retry 3× | Mark `extension_status: api_error`; publish book period only |</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>| Splice gap (book ends Q4 2012, FRED starts mid-year) | overlap check | Walk back to 2012Q1 / 2011Q4 anchor; if no overlap, fails hard |</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>| FRED unit drift (percent vs decimal) | sanity assertion `0.05 &lt; median &lt; 0.25` | If outside band, log warning and skip the suspect rows |</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>| FOR &lt; DSR violation | post-merge assertion | Log year/quarter; do NOT auto-correct |</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>| FRED_API_KEY missing | startup | Extension skipped; book quarterly published only |</t>
-        </is>
-      </c>
+      <c r="A151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>| TDSP / FODSP 5xx | retry 3× | Mark `extension_status: api_error`; publish book period only |</t>
+          <t>## 8. CD2 divergence</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>| Splice gap (book ends Q4 2012, FRED starts mid-year) | overlap check | Walk back to 2012Q1 / 2011Q4 anchor; if no overlap, fails hard |</t>
-        </is>
-      </c>
+      <c r="A153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>| FRED unit drift (percent vs decimal) | sanity assertion `0.05 &lt; median &lt; 0.25` | If outside band, log warning and skip the suspect rows |</t>
+          <t>CD2's `S101` decomposed into A (FOR) and B (DSR). RSCD S1606 preserves this naming and adds extension subseries C/D plus the annual variant E. Values on the book period should match CD2 within 0.1% (both pull from the same Fed publication).</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>| FOR &lt; DSR violation | post-merge assertion | Log year/quarter; do NOT auto-correct |</t>
-        </is>
-      </c>
+      <c r="A155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>## 9. Splice diagnostics (V03)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>## 8. CD2 divergence</t>
-        </is>
-      </c>
+      <c r="A157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>- Per-quarter MAE on book period 1980Q1-2012Q4 vs Appendix 16.2 columns — expected ~0%</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CD2's `S101` decomposed into A (FOR) and B (DSR). RSCD S1606 preserves this naming and adds extension subseries C/D plus the annual variant E. Values on the book period should match CD2 within 0.1% (both pull from the same Fed publication).</t>
+          <t>- Splice continuity 2012Q4 -&gt; 2013Q1: FRED value should match book value within ±0.5%</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>- Sample quarters (per CD2 S101 validation): 1980Q1, 1985Q1, 2000Q1, 2007Q1, 2012Q1</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>## 9. Splice diagnostics (V03)</t>
+          <t>- FOR &gt; DSR ordering: assertion at every quarter</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>- Per-quarter MAE on book period 1980Q1-2012Q4 vs Appendix 16.2 columns — expected ~0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>- Splice continuity 2012Q4 -&gt; 2013Q1: FRED value should match book value within ±0.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>- Sample quarters (per CD2 S101 validation): 1980Q1, 1985Q1, 2000Q1, 2007Q1, 2012Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>- FOR &gt; DSR ordering: assertion at every quarter</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A162" t="inlineStr">
         <is>
           <t>- Annual variant validation: exact arithmetic mean of corresponding quarters</t>
         </is>
@@ -3886,7 +3847,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-19T00:20:06.805239+00:00</t>
+          <t>2026-07-02T06:20:33.871332+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1606_extenbook.xlsx
+++ b/extenbooks/S1606_extenbook.xlsx
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:20:33.871332+00:00</t>
+          <t>2026-07-11T03:44:23.813679+00:00</t>
         </is>
       </c>
     </row>
@@ -3862,11 +3862,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3889,6 +3889,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_16_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "KB-verified: figure 16.10 caption and in-text passage (p.735) match; Federal Reserve FOR/DSR quarterly SA sourcing confirmed; verbatim quotes match.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1606_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1606_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FOR &gt; DSR by construction (FOR adds rent, leases, insurance, property tax).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>decimal_quarterly_and_decimal_annual_mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
